--- a/ET-release8.1/Unity/Assets/Config/Excel/BulletConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/BulletConfig.xlsx
@@ -14,20 +14,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="26">
   <si>
     <t>Id</t>
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>形状</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>Shape</t>
-    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>形状参数</t>
@@ -495,45 +487,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="C2:M6"/>
+  <dimension ref="C2:L6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.125" style="2" customWidth="1"/>
     <col min="2" max="2" width="12.75" style="2" customWidth="1"/>
     <col min="3" max="4" width="12.625" style="2" customWidth="1"/>
-    <col min="5" max="5" width="9" style="2"/>
-    <col min="6" max="6" width="11.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="11.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="13.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="5" max="5" width="11.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="11.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="13.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="3:12" x14ac:dyDescent="0.3">
       <c r="D2" s="2" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
-    <row r="3" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="3" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C3" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I3" s="3" t="s">
         <v>11</v>
@@ -547,28 +538,25 @@
       <c r="L3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="M3" s="3" t="s">
-        <v>19</v>
-      </c>
     </row>
-    <row r="4" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="4" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C4" s="3" t="s">
         <v>0</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>27</v>
+        <v>4</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I4" s="3" t="s">
         <v>12</v>
@@ -582,51 +570,45 @@
       <c r="L4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="M4" s="3" t="s">
-        <v>20</v>
-      </c>
     </row>
-    <row r="5" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C5" s="3" t="s">
         <v>1</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="3" t="s">
-        <v>5</v>
-      </c>
       <c r="G5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H5" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="3" t="s">
-        <v>10</v>
-      </c>
       <c r="I5" s="3" t="s">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
-    <row r="6" spans="3:13" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
         <v>3000001</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/ET-release8.1/Unity/Assets/Config/Excel/BulletConfig.xlsx
+++ b/ET-release8.1/Unity/Assets/Config/Excel/BulletConfig.xlsx
@@ -605,7 +605,7 @@
     </row>
     <row r="6" spans="3:12" x14ac:dyDescent="0.3">
       <c r="C6" s="1">
-        <v>3000001</v>
+        <v>30001</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>24</v>
